--- a/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T1448_W0038F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.24022964139018</v>
+        <v>4.426537316725905</v>
       </c>
       <c r="D2" t="n">
-        <v>23.77063448404004</v>
+        <v>3.862728103656507</v>
       </c>
       <c r="E2" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F2" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.39980637814539</v>
+        <v>4.777468536448626</v>
       </c>
       <c r="D3" t="n">
-        <v>15.15722236629895</v>
+        <v>2.463048634523579</v>
       </c>
       <c r="E3" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F3" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>60.37045913988845</v>
+        <v>9.810199610231875</v>
       </c>
       <c r="D4" t="n">
-        <v>20.06283685694005</v>
+        <v>3.260210989252757</v>
       </c>
       <c r="E4" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F4" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.21909640249</v>
+        <v>6.210603165404626</v>
       </c>
       <c r="D5" t="n">
-        <v>4.346924555648051</v>
+        <v>0.7063752402928083</v>
       </c>
       <c r="E5" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F5" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>50.32701900765765</v>
+        <v>8.178140588744368</v>
       </c>
       <c r="D6" t="n">
-        <v>21.65063720342183</v>
+        <v>3.518228545556047</v>
       </c>
       <c r="E6" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F6" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>42.67860411857665</v>
+        <v>6.935273169268706</v>
       </c>
       <c r="D7" t="n">
-        <v>47.57386449704221</v>
+        <v>7.730752980769359</v>
       </c>
       <c r="E7" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F7" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.94187291051582</v>
+        <v>2.915554347958821</v>
       </c>
       <c r="D8" t="n">
-        <v>10.89334969820608</v>
+        <v>1.770169325958489</v>
       </c>
       <c r="E8" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F8" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>17.43900763295026</v>
+        <v>2.833838740354418</v>
       </c>
       <c r="D9" t="n">
-        <v>16.88497877277428</v>
+        <v>2.743809050575821</v>
       </c>
       <c r="E9" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F9" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>26.86392762532445</v>
+        <v>4.365388239115223</v>
       </c>
       <c r="D10" t="n">
-        <v>6.778921298067146</v>
+        <v>1.101574710935911</v>
       </c>
       <c r="E10" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F10" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.26960436459534</v>
+        <v>2.806310709246743</v>
       </c>
       <c r="D11" t="n">
-        <v>5.064088395377406</v>
+        <v>0.8229143642488286</v>
       </c>
       <c r="E11" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F11" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>38.34618784771574</v>
+        <v>6.231255525253808</v>
       </c>
       <c r="D12" t="n">
-        <v>54.12027902954095</v>
+        <v>8.794545342300404</v>
       </c>
       <c r="E12" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F12" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>13.16041310221862</v>
+        <v>2.138567129110526</v>
       </c>
       <c r="D13" t="n">
-        <v>13.85030412558584</v>
+        <v>2.250674420407698</v>
       </c>
       <c r="E13" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F13" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>16.37060713026215</v>
+        <v>2.6602236586676</v>
       </c>
       <c r="D14" t="n">
-        <v>17.14539905092139</v>
+        <v>2.786127345774727</v>
       </c>
       <c r="E14" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F14" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>37.46750865256985</v>
+        <v>6.088470156042602</v>
       </c>
       <c r="D15" t="n">
-        <v>72.54117050944112</v>
+        <v>11.78794020778418</v>
       </c>
       <c r="E15" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F15" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>29.81756940297744</v>
+        <v>4.845355027983834</v>
       </c>
       <c r="D16" t="n">
-        <v>30.7459681622961</v>
+        <v>4.996219826373117</v>
       </c>
       <c r="E16" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F16" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>34.50758682717671</v>
+        <v>5.607482859416216</v>
       </c>
       <c r="D17" t="n">
-        <v>35.45745619701133</v>
+        <v>5.761836632014342</v>
       </c>
       <c r="E17" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F17" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>19.73220302824244</v>
+        <v>3.206482992089397</v>
       </c>
       <c r="D18" t="n">
-        <v>54.72004819489276</v>
+        <v>8.892007831670075</v>
       </c>
       <c r="E18" t="n">
-        <v>12.75200029036017</v>
+        <v>2.072200047183528</v>
       </c>
       <c r="F18" t="n">
-        <v>19.31958349531102</v>
+        <v>3.139432317988041</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
